--- a/光伏配储项目/电价数据/2026/石城站.xlsx
+++ b/光伏配储项目/电价数据/2026/石城站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50989</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.71985</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5646</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5154299999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45296</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44759</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45468</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42326</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42341</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44426</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26777</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21344</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.25788</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07651000000000001</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06283</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05082</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03131</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05248</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03895000000000001</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04415</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.00694</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.01935</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08617</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01435</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.00224</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00351</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14521</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21297</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23614</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.11409</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.00578</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00701</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.1537</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.18968</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22259</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.02393</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.12176</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.1929</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.26039</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.01361</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.23051</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.02104</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.52727</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.48302</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.76255</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61497</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.51127</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.50966</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.13201</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5870599999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5420199999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.26578</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.5003</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.50339</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.61497</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.57125</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43338</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.43536</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.34383</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6235599999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.42948</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.75658</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.3453</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9768600000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.54569</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5276000000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51547</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.5112099999999999</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47727</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38203</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42536</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5281699999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6545599999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.75187</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44273</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.16234</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44767</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.08851000000000001</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.04627000000000001</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.21579</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.13269</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.26865</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.25713</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.58997</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.21069</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.27612</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.29307</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.27021</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.58262</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.39097</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.01907</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.26779</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.26923</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.23031</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.15903</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.23296</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.25882</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23149</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27223</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.43826</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.42301</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.26649</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.47165</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.28422</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.70869</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.04476</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.9408300000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.26943</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.84626</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.43041</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.82478</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43825</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.59848</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43915</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43382</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40786</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.30173</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5872000000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47393</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.28951</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.2704</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.26837</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.28063</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.26461</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.26271</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.25896</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44852</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44289</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.29191</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28456</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.15226</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.26896</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.28045</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.06999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.21606</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.14765</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.20581</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.1931</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.2479</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.27723</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.28779</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.24714</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.21501</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.0491</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.28224</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.4782</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.01775</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.50041</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.28806</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.28772</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34409</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.27122</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.2746499999999999</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47882</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.29177</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.27466</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.29905</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.28171</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.28034</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.2809700000000001</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.29904</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.27967</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26221</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26392</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.19387</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.10813</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11164</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08137999999999999</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.2506</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.21244</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.13072</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.44828</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.21282</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.04502</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.04593</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06117</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.26975</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.17626</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.04137</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.01006</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21301</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.00121</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.03086</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.07693999999999999</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.20269</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.16673</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.2036</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.15201</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19636</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14253</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.20045</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.22772</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.27932</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.25741</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28676</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.4702</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.25586</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29218</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28985</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29216</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30034</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.29839</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.27564</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.27399</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.27676</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26047</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04072</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04515</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04026</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04001</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04269</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04504</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04354</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04555</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04634000000000001</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04711</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04789</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04639</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04672</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04757</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04678</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04795</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04989</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04645000000000001</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04792</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04913</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04873</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04643</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04729999999999999</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22003</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04645000000000001</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04893</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00213</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14708</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03757</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09886</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.36741</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39547</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41227</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41731</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35132</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6644099999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44655</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10243</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04263</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04591</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.0451</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04401</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04182</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03235</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04069</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10694</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00107</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03741</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04688000000000001</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.0411</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04127</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04119</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04368</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04357</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04108</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04049000000000001</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04328</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04034</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03897</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04401</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04108</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04216</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.03997999999999999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04265</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04306</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04644</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04602000000000001</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20234</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14481</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29971</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33775</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32291</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40737</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28357</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29786</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27352</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27367</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17436</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.16062</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17325</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14959</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16131</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.16069</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2396</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21612</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22872</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27199</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28332</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27085</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28319</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.25918</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.23518</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.25626</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>-0.04747999999999999</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.27456</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.24807</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.24923</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.28332</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15729</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.15245</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.2805299999999999</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.2591</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.27915</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7910900000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78086</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.9200199999999999</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4943</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.9066900000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31938</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9298200000000001</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6387699999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.22867</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8893799999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5805</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.37349</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.06219</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.57357</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.82733</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.80953</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.8065099999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.88127</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8929600000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5272899999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.43201</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.44372</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.48891</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.25083</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.88007</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55177</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.66534</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54915</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.5102</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46115</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42939</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44483</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45202</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45326</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42237</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39676</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43438</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3762200000000001</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4137</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45133</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58968</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42854</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59685</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60199</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.64495</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45471</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44738</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86503</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.05501</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.57664</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.5607300000000001</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.7419199999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.19731</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.4342200000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.24768</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27329</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30152</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35329</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.02489</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.49943</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.50129</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.6194700000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.6938200000000001</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41497</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.44967</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.5109</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.44789</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28067</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16473</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26108</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20118</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27747</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29163</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27593</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.28674</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.25227</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.21672</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.28581</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.27463</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29103</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.24945</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27495</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42822</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.24599</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44702</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59766</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88976</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35746</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.1366</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7117599999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8057799999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6512899999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59088</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45102</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50043</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43989</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42367</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5009</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43407</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43409</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43442</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.21996</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.22756</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.26047</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.23959</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.2293</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.22263</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.23073</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.21623</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.23306</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.06153</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.22287</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.21221</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.01943</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.23788</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.26718</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.26094</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.2365</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>-0.01455</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.22287</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26855</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.16556</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.23756</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.48621</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.4312</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.60748</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46572</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.6848500000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46672</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4396</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42561</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32653</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42572</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39372</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.28546</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29203</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29407</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23719</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14919</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15614</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14234</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14484</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14376</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25894</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14547</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26867</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26879</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14334</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05287</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11479</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11373</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14757</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14254</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14778</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.26211</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.28361</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.28444</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45141</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40364</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44181</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44125</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4462</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44546</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40426</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35069</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47035</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42543</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39464</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.26234</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.22441</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.22472</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.2167</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.14503</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.05444</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.10974</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.16187</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.14079</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.15952</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.16971</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.14238</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.17435</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.17134</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.2606</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.26537</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44608</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.4589</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24932</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.42557</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.51163</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36064</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39229</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28448</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.21855</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.23589</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.2407</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26973</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.2533</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03329</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25437</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24999</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.20985</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07490999999999999</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18423</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24494</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.27098</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25304</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27439</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42785</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.50534</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41599</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7767999999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.45008</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46801</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.43474</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41712</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31003</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.26755</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.2695</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.26999</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28262</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28746</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.27778</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34408</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.73421</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.4157</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42956</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40735</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39165</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6495599999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.87642</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48718</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.48541</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46041</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34507</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26143</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29123</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19528</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24635</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27857</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.02636</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.13043</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.01782</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28407</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23748</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24781</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.008750000000000001</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14503</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.02385</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.23359</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23649</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40858</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.61773</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.59153</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.55592</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46226</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.5889099999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47781</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.7048</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45371</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.45992</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48175</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41997</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49336</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.47403</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46634</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.4573</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42151</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40104</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40745</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41396</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41138</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41977</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38803</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45081</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56133</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50093</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45097</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.41461</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41965</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42726</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.40316</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.24214</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.23506</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.13713</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.15249</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.04043</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.03249</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.1434</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>-0.00925</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.10649</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.00657</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.26876</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.03483</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48602</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50842</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.5668500000000001</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.63991</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.62412</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.58851</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.6448400000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.48799</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.48188</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.70443</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.65566</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.54327</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.5803200000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44809</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.44096</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.48996</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40822</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.42362</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.43528</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41894</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41129</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.43806</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40454</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.43749</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38347</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38416</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39459</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27881</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15834</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27273</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03783</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45299</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46396</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01526</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18512</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30463</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.39252</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.39593</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.3739</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36276</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44379</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.38424</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.62781</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.6624099999999999</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24835</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23547</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23717</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24609</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25191</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.03881</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.00128</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.10914</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.05567</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.17568</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25939</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.03888</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14855</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15243</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.05825</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.008529999999999999</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.08311</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>-0.03041</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.09886</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35065</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.1933</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.18636</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.13155</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.15052</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04604999999999999</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01615</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00151</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.04364</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04149</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.13943</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.19144</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27687</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2236</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22425</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.2251</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.22935</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.23972</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.24934</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24272</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2339</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.24991</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25356</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.23645</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.25472</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24332</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.2607</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.24865</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.26209</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.27626</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.27642</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.21863</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.23882</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.21684</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.18674</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.08624999999999999</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.0366</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.2418</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.04374</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.15747</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.15709</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.15742</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.02579</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.23421</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.21775</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.20208</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16616</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15839</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.13339</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.15817</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.18911</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.1105</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.12525</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.19163</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.16119</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.21119</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.18401</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.17165</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.22259</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.17146</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.22225</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.22915</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.21099</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.21772</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.13196</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.04144</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.4454</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.19999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.00114</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.17198</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.16805</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.02264</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18737</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.26675</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.08218</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.04556</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.01425</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.04573</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23462</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28056</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25238</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.19582</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32625</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.10572</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.27043</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.43771</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.25792</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25324</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.11865</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24291</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.28528</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.25285</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.27926</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.27632</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25639</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26982</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.18881</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14349</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.10478</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39667</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33213</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.24123</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.26432</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38429</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.12245</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.15463</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.25517</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.27364</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.28179</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.26715</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.17341</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26139</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38428</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.26559</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26653</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26303</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24753</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28233</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.28169</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.24059</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.40792</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.19077</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.22081</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.5217000000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.01353</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.41465</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.45975</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.51007</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40496</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5463300000000001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.47703</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45472</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43119</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.81116</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.4987799999999999</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42825</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.4404</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40296</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36903</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46757</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.28959</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.46051</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.20824</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.17678</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23467</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.24766</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.26929</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.27117</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.26105</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19303</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.29502</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.26537</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.29045</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.27782</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.50615</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41442</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46599</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.56024</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.56904</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46205</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5518099999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46494</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49751</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.53289</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.5206499999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.68198</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.72814</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55015</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5528099999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44491</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39117</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37685</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27247</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.26845</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.28004</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.26732</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25548</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.24863</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.23852</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.23719</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.25427</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.1903</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.21241</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.13396</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.0055</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.04269</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.12797</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01252</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02295</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.02533</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23539</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.01604</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02159</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03131</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02204</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01493</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01804</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.10483</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06401999999999999</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11922</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.13763</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.16528</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22324</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.1813</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.18562</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.20783</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.25025</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38742</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.4049700000000001</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38073</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.72665</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38403</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.27644</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27142</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.26116</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.23283</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.2265</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.19558</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.19557</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.19998</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.2161</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.02405</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.02622</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.0268</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03614</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.07840000000000001</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04433</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.01707</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.01739</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.01076</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.1555</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.03434</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>-0.03389</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.01985</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.2252</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.18285</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.23512</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.26837</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42932</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38259</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5280499999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39769</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.4085299999999999</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43151</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39211</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38188</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.51225</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.23209</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.18695</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.17208</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.11276</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.14821</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.17464</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.16207</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.08733</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.10439</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04745000000000001</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.07006999999999999</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03775</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03651</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04532</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05163</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.05977</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03472</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05668</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.07179000000000001</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11452</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.14238</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08641</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.16331</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.14471</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.08925</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04611999999999999</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21462</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.09568</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.09115999999999999</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.18705</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.13012</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.1406</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.16659</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.14629</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.18101</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.19999</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.20102</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.21381</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25502</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.25895</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.2605</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.2825299999999999</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40393</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.27325</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.41333</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.4199</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49766</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40987</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41827</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44312</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41519</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39741</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.41551</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41466</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38219</v>
       </c>
     </row>
   </sheetData>
